--- a/assets/data/excel/reputation.xlsx
+++ b/assets/data/excel/reputation.xlsx
@@ -1,61 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="声誉等级" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="声望等级" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="声望获取" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -63,32 +43,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -235,7 +200,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -270,7 +234,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -305,16 +268,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -436,46 +403,7 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -486,643 +414,1336 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>requiredPoints</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>unlockFacility</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>unlockEnergy</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>unlockCharacter</t>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>expRequired</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>unlockMap</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>unlockZone</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>unlockContent</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>等级</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>所需点数</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>解锁设施</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>解锁能量</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>解锁角色</t>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>升级所需经验</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>解锁地图</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>解锁区域</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>解锁内容</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>见习驾驶员</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>庇护所外围</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>设施2级</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>活力苏打</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>⭐普通</t>
-        </is>
-      </c>
+          <t>ZONE_SANCTUARY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>新手拾荒者</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>基础</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>普通能量</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>⭐普通</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>正式队员</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>300</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>设施3级</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>强力能量,精准燃料</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>⭐⭐中级</t>
-        </is>
-      </c>
+      <c r="B6" t="n">
+        <v>99</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>见习驾驶员</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>设施2级</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>活力苏打</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>⭐普通</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B7" t="n">
+        <v>105</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>资深探险家</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>600</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>设施4级</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>112</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>精准燃料</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>⭐⭐中级</t>
+          <t>解锁每日辐射区探索</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>正式队员</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>300</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>设施3级</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>强力能量,精准燃料</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>⭐⭐中级</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B9" t="n">
+        <v>118</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>队长</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>设施5级,黑客终端</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>超频能量,战意激化剂,守护合剂</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐高级</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B10" t="n">
+        <v>124</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>资深探险家</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>600</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>设施4级</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>精准燃料</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>⭐⭐中级</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B11" t="n">
+        <v>131</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>英雄</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>设施6级</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>战意激化剂,守护合剂</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐高级</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B12" t="n">
+        <v>137</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>队长</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>设施5级,黑客终端</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>超频能量,战意激化剂,守护合剂</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐高级</t>
+          <t>解锁装备强化系统</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>传奇人物</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2500</v>
+        <v>11</v>
+      </c>
+      <c r="B14" t="n">
+        <v>151</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>废弃矿区</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>设施7级</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>传说能量</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐传说</t>
-        </is>
-      </c>
+          <t>ZONE_MINE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>英雄</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>设施6级</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>战意激化剂,守护合剂</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐高级</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B15" t="n">
+        <v>162</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>废土领袖</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>设施8级</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>传说能量,源初精华</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐传说</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B16" t="n">
+        <v>173</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>传奇人物</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>设施7级</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>传说能量</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐传说</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B17" t="n">
+        <v>184</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>方舟使者</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>6000</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>设施9级</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B18" t="n">
+        <v>196</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>源初精华,禁忌药剂</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐传说</t>
+          <t>解锁融合姬突破系统</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>8</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>废土领袖</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>设施8级</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>传说能量,源初精华</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐传说</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="B19" t="n">
+        <v>207</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>传奇永恒</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>设施满级</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>禁忌药剂</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>全部品质</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="B20" t="n">
+        <v>218</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>9</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>方舟使者</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>6000</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>设施9级</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>源初精华,禁忌药剂</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐传说</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
+        <v>18</v>
+      </c>
+      <c r="B21" t="n">
+        <v>229</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" t="n">
+        <v>240</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+    </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>10</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>传奇永恒</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>设施满级</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B23" t="n">
+        <v>140</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>禁忌药剂</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>全部品质</t>
+          <t>解锁竞技场</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" t="n">
+        <v>216</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>沉没水城</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ZONE_AQUA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" t="n">
+        <v>231</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" t="n">
+        <v>248</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" t="n">
+        <v>264</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" t="n">
+        <v>280</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>解锁芯片镶嵌系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" t="n">
+        <v>296</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" t="n">
+        <v>312</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" t="n">
+        <v>328</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" t="n">
+        <v>344</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" t="n">
+        <v>200</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>解锁公会系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" t="n">
+        <v>280</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>腐化丛林</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ZONE_TREE</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" t="n">
+        <v>301</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" t="n">
+        <v>322</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" t="n">
+        <v>343</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" t="n">
+        <v>364</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>解锁融合姬觉醒任务</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" t="n">
+        <v>384</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" t="n">
+        <v>405</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" t="n">
+        <v>426</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" t="n">
+        <v>447</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" t="n">
+        <v>260</v>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>解锁深渊副本</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" t="n">
+        <v>345</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>深海遗迹</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ZONE_DEEP</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" t="n">
+        <v>371</v>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" t="n">
+        <v>396</v>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" t="n">
+        <v>422</v>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" t="n">
+        <v>448</v>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>解锁源核商店高级兑换</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" t="n">
+        <v>473</v>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" t="n">
+        <v>499</v>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" t="n">
+        <v>524</v>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" t="n">
+        <v>550</v>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" t="n">
+        <v>320</v>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>解锁跨服竞技</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" t="n">
+        <v>410</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>军事要塞</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ZONE_HQ</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" t="n">
+        <v>440</v>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" t="n">
+        <v>471</v>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" t="n">
+        <v>501</v>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" t="n">
+        <v>532</v>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>解锁传说装备锻造</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" t="n">
+        <v>562</v>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" t="n">
+        <v>592</v>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" t="n">
+        <v>623</v>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" t="n">
+        <v>653</v>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" t="n">
+        <v>380</v>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>解锁赛季挑战</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" t="n">
+        <v>475</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>荧光温泉</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ZONE_SPRING</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" t="n">
+        <v>510</v>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" t="n">
+        <v>545</v>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" t="n">
+        <v>580</v>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" t="n">
+        <v>616</v>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>解锁融合姬终极进化</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" t="n">
+        <v>651</v>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" t="n">
+        <v>686</v>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" t="n">
+        <v>721</v>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" t="n">
+        <v>756</v>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" t="n">
+        <v>440</v>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>解锁世界Boss</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" t="n">
+        <v>540</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>机械军火库</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ZONE_ARSENAL</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" t="n">
+        <v>580</v>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" t="n">
+        <v>620</v>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" t="n">
+        <v>660</v>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" t="n">
+        <v>700</v>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>解锁传说级融合姬召唤</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" t="n">
+        <v>740</v>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" t="n">
+        <v>780</v>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" t="n">
+        <v>820</v>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" t="n">
+        <v>860</v>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" t="n">
+        <v>500</v>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>解锁终局副本</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" t="n">
+        <v>604</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>方舟核心</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ZONE_CORE</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" t="n">
+        <v>649</v>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" t="n">
+        <v>694</v>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" t="n">
+        <v>739</v>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" t="n">
+        <v>784</v>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>解锁UR品质装备掉落</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" t="n">
+        <v>828</v>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>87</v>
+      </c>
+      <c r="B90" t="n">
+        <v>873</v>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>88</v>
+      </c>
+      <c r="B91" t="n">
+        <v>918</v>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>89</v>
+      </c>
+      <c r="B92" t="n">
+        <v>963</v>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>90</v>
+      </c>
+      <c r="B93" t="n">
+        <v>560</v>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>解锁辐射风暴</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>91</v>
+      </c>
+      <c r="B94" t="n">
+        <v>669</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>终焉之地</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ZONE_OMEGA</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>92</v>
+      </c>
+      <c r="B95" t="n">
+        <v>719</v>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>93</v>
+      </c>
+      <c r="B96" t="n">
+        <v>768</v>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>94</v>
+      </c>
+      <c r="B97" t="n">
+        <v>818</v>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>95</v>
+      </c>
+      <c r="B98" t="n">
+        <v>868</v>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>解锁LE品质融合姬碎片</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>96</v>
+      </c>
+      <c r="B99" t="n">
+        <v>917</v>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>97</v>
+      </c>
+      <c r="B100" t="n">
+        <v>967</v>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>98</v>
+      </c>
+      <c r="B101" t="n">
+        <v>1016</v>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>99</v>
+      </c>
+      <c r="B102" t="n">
+        <v>1066</v>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>达到满级，解锁全内容</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1906,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>招募新角色</t>
+          <t>招募新融合姬</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1331,7 +1952,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>使用能量饮料</t>
+          <t>完成禁区探索</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1347,7 +1968,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>每日首次使用额外+5</t>
+          <t>每日首次完成额外+5</t>
         </is>
       </c>
     </row>
